--- a/maintenance/GenericLubrication_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/GenericLubrication_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,26 @@
           <t>Last Done Furnace Hours</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Required Parts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Planning months</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated duration min</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +633,22 @@
       <c r="T2" t="n">
         <v>0</v>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -697,6 +733,22 @@
       <c r="T3" t="n">
         <v>0</v>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -781,6 +833,22 @@
       <c r="T4" t="n">
         <v>0</v>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Grease (NLGI-2)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -865,6 +933,22 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>6-Month</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>6</v>
+      </c>
+      <c r="X5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -949,6 +1033,22 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1033,6 +1133,22 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Applicator seal kit; Light machine oil</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1117,6 +1233,22 @@
       <c r="T8" t="n">
         <v>0</v>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1201,6 +1333,22 @@
       <c r="T9" t="n">
         <v>0</v>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1285,6 +1433,22 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1369,6 +1533,22 @@
       <c r="T11" t="n">
         <v>0</v>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1452,6 +1632,22 @@
       </c>
       <c r="T12" t="n">
         <v>0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Grease (NLGI-2)</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/maintenance/GenericLubrication_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/GenericLubrication_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,26 @@
           <t>Estimated duration min</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Last_Done_Draw</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV1</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_Furnace</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -589,7 +609,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>days</t>
@@ -621,14 +640,10 @@
           <t>Shielded/sealed-for-life bearings must NOT be lubricated.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
+          <t>2026-03-27</t>
+        </is>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -689,7 +704,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>months</t>
@@ -721,14 +735,10 @@
           <t>Apply sparingly; remove excess oil.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
+          <t>2026-03-08</t>
+        </is>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -789,7 +799,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>months</t>
@@ -821,14 +830,10 @@
           <t>Do not over-grease.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
+          <t>2026-02-04</t>
+        </is>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -889,7 +894,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>months</t>
@@ -921,14 +925,10 @@
           <t>Thin film only.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
+          <t>2025-09-29</t>
+        </is>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -989,7 +989,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>weeks</t>
@@ -1021,14 +1020,10 @@
           <t>Avoid oil contamination of fibre.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
+          <t>2026-03-29</t>
+        </is>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1089,7 +1084,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>months</t>
@@ -1121,14 +1115,10 @@
           <t>Apply sparingly.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
+          <t>2026-03-08</t>
+        </is>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1189,7 +1179,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>months</t>
@@ -1221,14 +1210,10 @@
           <t>Avoid oil migration into gas path.</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
+          <t>2026-03-17</t>
+        </is>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1289,7 +1274,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>months</t>
@@ -1321,14 +1305,10 @@
           <t>Do not lubricate sealed bearings.</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
+          <t>2026-03-08</t>
+        </is>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1389,7 +1369,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>months</t>
@@ -1421,14 +1400,10 @@
           <t>Sealed-for-life bearings must not be lubricated.</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
+          <t>2026-03-17</t>
+        </is>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1489,7 +1464,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>months</t>
@@ -1521,14 +1495,10 @@
           <t>Remove surplus oil before operation.</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
+          <t>2026-03-17</t>
+        </is>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1589,7 +1559,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>months</t>
@@ -1621,14 +1590,10 @@
           <t>Do not over-grease.</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
+          <t>2026-02-04</t>
+        </is>
       </c>
       <c r="T12" t="n">
         <v>0</v>
